--- a/Excel/CELLULAR-NEW.xlsx
+++ b/Excel/CELLULAR-NEW.xlsx
@@ -5,22 +5,23 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NGODING\BOOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NGODING\BOOS\BOOS\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3446E8C-65AB-4258-B5C0-C196057021B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7E3288-0D62-4C97-95B1-A4954AFE9782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{D629B100-6E31-4C56-8C6E-B41B92F478BA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629B100-6E31-4C56-8C6E-B41B92F478BA}"/>
   </bookViews>
   <sheets>
-    <sheet name="5980-SYDIB-HC-253651" sheetId="1" r:id="rId1"/>
+    <sheet name="FORM" sheetId="1" r:id="rId1"/>
+    <sheet name="DATA" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
   <si>
     <t>BLIND TYPE</t>
   </si>
@@ -37,18 +38,6 @@
     <t>DROP</t>
   </si>
   <si>
-    <t>CS MATERIAL SIZE</t>
-  </si>
-  <si>
-    <t>CS MATERIAL COLOUR</t>
-  </si>
-  <si>
-    <t>CS MATERIAL SIZE B</t>
-  </si>
-  <si>
-    <t>CS MATERIAL COLOUR B</t>
-  </si>
-  <si>
     <t>HOLD DOWN CLIP</t>
   </si>
   <si>
@@ -61,9 +50,6 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>front door right</t>
-  </si>
-  <si>
     <t xml:space="preserve">Notes: </t>
   </si>
   <si>
@@ -76,9 +62,6 @@
     <t>Left</t>
   </si>
   <si>
-    <t>Your Note</t>
-  </si>
-  <si>
     <t>ORDER NUMBER</t>
   </si>
   <si>
@@ -112,7 +95,52 @@
     <t>Opening Size Reveal Fit</t>
   </si>
   <si>
+    <t>Your Order Number</t>
+  </si>
+  <si>
+    <t>Your Order Name</t>
+  </si>
+  <si>
+    <t>Your Order Note</t>
+  </si>
+  <si>
+    <t>Room 1</t>
+  </si>
+  <si>
+    <t>FABRIC TYPE</t>
+  </si>
+  <si>
+    <t>FABRIC COLOUR</t>
+  </si>
+  <si>
+    <t>FABRIC TYPE B</t>
+  </si>
+  <si>
+    <t>FABRIC COLOUR B</t>
+  </si>
+  <si>
+    <t>Top Down Bottom Up</t>
+  </si>
+  <si>
     <t>Cordless</t>
+  </si>
+  <si>
+    <t>Alabaster (Regular)</t>
+  </si>
+  <si>
+    <t>Both Sides</t>
+  </si>
+  <si>
+    <t>Day &amp; Night</t>
+  </si>
+  <si>
+    <t>Opening Size Face Fit</t>
+  </si>
+  <si>
+    <t>Make Size Face Fit</t>
+  </si>
+  <si>
+    <t>Make Size Reveal Fit</t>
   </si>
 </sst>
 </file>
@@ -255,7 +283,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -433,6 +461,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -596,8 +630,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -953,174 +991,324 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAEA6248-CABD-441C-8A59-6B502B6C5A85}">
-  <dimension ref="A1:P51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" customWidth="1"/>
-    <col min="6" max="6" width="24.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" customWidth="1"/>
-    <col min="9" max="9" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" customWidth="1"/>
+    <col min="6" max="6" width="24.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" customWidth="1"/>
+    <col min="9" max="9" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="N3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>12345678</v>
-      </c>
-      <c r="B2">
-        <v>12345678</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" t="s">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="L3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O3" t="s">
-        <v>9</v>
-      </c>
-      <c r="P3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="H4">
-        <v>2035</v>
+        <v>1000</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="O4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
         <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="H5">
-        <v>2035</v>
+        <v>1000</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="M5" t="s">
+        <v>35</v>
+      </c>
+      <c r="O5" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>14</v>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6">
+        <v>1000</v>
+      </c>
+      <c r="H6">
+        <v>1000</v>
+      </c>
+      <c r="I6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C231DF-0195-41AE-9CFD-B64228CEDC15}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" customWidth="1"/>
+    <col min="3" max="3" width="15.21875" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>